--- a/data/trans_dic/IP31AA_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31AA_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que se cepillan los dientes una o ninguna vez al día</t>
+          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,49; 65,72</t>
+          <t>32,27; 65,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,47; 62,74</t>
+          <t>37,5; 60,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,79; 59,38</t>
+          <t>38,83; 58,77</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,29; 46,79</t>
+          <t>28,59; 46,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,52; 39,94</t>
+          <t>30,59; 39,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,03; 41,13</t>
+          <t>31,01; 40,82</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,45; 35,0</t>
+          <t>23,88; 36,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,75; 36,91</t>
+          <t>24,08; 37,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,66; 34,27</t>
+          <t>25,32; 34,03</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,55; 43,64</t>
+          <t>29,57; 42,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,8; 38,9</t>
+          <t>31,6; 38,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,61; 39,34</t>
+          <t>31,89; 38,85</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>24553</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27725</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52278</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>17064; 34410</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20725; 33548</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42001; 63558</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>152790</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>176738</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>329528</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>128726; 210120</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>153924; 200532</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>295660; 389174</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>42384</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54685</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>97069</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>34547; 52446</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43612; 67341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82490; 110891</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>219727</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>259149</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>478876</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>191536; 273064</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>233724; 285727</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>442414; 538991</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>